--- a/Salaray_Breakdown_Analysis.xlsx
+++ b/Salaray_Breakdown_Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE71685-D80C-4DE7-93B8-E481C896C4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE46F66-6841-4CC3-A063-6748F8F0331E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1830" windowWidth="30285" windowHeight="15345" xr2:uid="{5DEC0479-A997-4C84-988A-5D2FAA7FE317}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13740" xr2:uid="{5DEC0479-A997-4C84-988A-5D2FAA7FE317}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -44,12 +33,21 @@
     <author>tc={F50BBF3F-D9D3-4EB8-A86E-E0EDA2A47EAD}</author>
   </authors>
   <commentList>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{F50BBF3F-D9D3-4EB8-A86E-E0EDA2A47EAD}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{F50BBF3F-D9D3-4EB8-A86E-E0EDA2A47EAD}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Non-linear accumulation equation</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -57,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Fuel economy (mile / gal)</t>
   </si>
@@ -118,6 +116,9 @@
   </si>
   <si>
     <t>Weekly pay ($)</t>
+  </si>
+  <si>
+    <t>Daily commute (minutes)</t>
   </si>
 </sst>
 </file>
@@ -161,7 +162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -183,17 +184,26 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -202,27 +212,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="40" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="40" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="40" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="40" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD21BCDC-0F36-4605-9774-C1621DC87D5B}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
@@ -583,141 +605,205 @@
     <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
       <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9">
         <v>4.5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="9">
         <f>45*2</f>
         <v>90</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="G2" s="11">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="12">
         <v>130000</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="K2" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="8">
         <v>42</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="6">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="C3" s="10">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="8">
+        <f>50*2</f>
+        <v>100</v>
+      </c>
+      <c r="G3" s="10">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <f>J2/2080</f>
         <v>62.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="K3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="9">
         <v>3000</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4">
-        <f>F2*F3*52</f>
-        <v>23400</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="C4" s="11">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="9">
+        <v>5</v>
+      </c>
+      <c r="G4" s="11">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="8">
         <f>(((4.2/12)*60)*4.2)+15</f>
         <v>103.20000000000002</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8">
+        <f>F2*F4*52</f>
+        <v>23400</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1200</v>
+      </c>
+      <c r="K5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9">
+        <v>650</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F6" s="9">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="G6" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8">
+        <v>75000</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9">
         <v>1200</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="8">
         <v>60000</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="9">
         <f>40/4</f>
         <v>10</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Salaray_Breakdown_Analysis.xlsx
+++ b/Salaray_Breakdown_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE46F66-6841-4CC3-A063-6748F8F0331E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE690B4-F8EC-4013-8D9F-C46E10528A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13740" xr2:uid="{5DEC0479-A997-4C84-988A-5D2FAA7FE317}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Fuel economy (mile / gal)</t>
   </si>
@@ -119,13 +119,19 @@
   </si>
   <si>
     <t>Daily commute (minutes)</t>
+  </si>
+  <si>
+    <t>Amt</t>
+  </si>
+  <si>
+    <t>Include?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +142,14 @@
     <font>
       <b/>
       <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -162,7 +176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -208,43 +222,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="40" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="40" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="40" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="40" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="40" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="40" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="40" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,200 +641,212 @@
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="C2" s="11">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>4.8</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="6">
         <f>45*2</f>
         <v>90</v>
       </c>
-      <c r="G2" s="11">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="8">
         <v>130000</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>42</v>
       </c>
-      <c r="C3" s="10">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <f>50*2</f>
         <v>100</v>
       </c>
-      <c r="G3" s="10">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="9">
         <f>J2/2080</f>
         <v>62.5</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="6">
         <v>3000</v>
       </c>
-      <c r="C4" s="11">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>5</v>
       </c>
-      <c r="G4" s="11">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6" t="s">
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="11">
+      <c r="J4" s="10"/>
+      <c r="K4" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <f>(((4.2/12)*60)*4.2)+15</f>
         <v>103.20000000000002</v>
       </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <f>F2*F4*52</f>
         <v>23400</v>
       </c>
-      <c r="G5" s="10">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="9">
+        <f>J2*0.01</f>
+        <v>1300</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6">
+        <v>650</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7">
+        <v>75000</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6">
         <v>1200</v>
       </c>
-      <c r="K5" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9">
-        <v>650</v>
-      </c>
-      <c r="C6" s="11">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8">
-        <v>75000</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9">
-        <v>1200</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="C8" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>60000</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9">
-        <f>40/4</f>
-        <v>10</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="6">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4">
         <v>0</v>
       </c>
     </row>
